--- a/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LNVGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>LNVGY</t>
   </si>
@@ -656,173 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,86 +870,92 @@
       <c r="O8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3">
         <v>15266600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>17089500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16955600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>16693800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>20126500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>17868700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>16929200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>15630100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>17245400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>14518900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>13347900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>10579400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14102800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>13522000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>12512200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>11710300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>14035100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>13379800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>11912700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>10638300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>12938500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>11760900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>10012200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>9578700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>12168700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>11231200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,86 +995,92 @@
       <c r="O9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3">
         <v>12654400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>14213000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>14086700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>13829500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>16771300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>14862900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>14105500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>12942200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>14459300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>12266400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>11306500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>8717600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>11838200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>11339400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>10463800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>9815100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>11985500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>11585700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>10281100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>9094300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>11187500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>10148400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>8647600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>8210200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>10573500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>9624000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1100,86 +1120,92 @@
       <c r="O10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3">
         <v>2612200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2876500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2868900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2864300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3355200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>3005800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>2823700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2687900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>2786100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>2252500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2041400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1861800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2264600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2182600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2048400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1895200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>2049600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1794100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1631600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1751000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>1612500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1364600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>1595200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>1607200</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1247,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1262,86 +1290,92 @@
       <c r="O12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3">
         <v>578600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>555700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>511400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>575800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>549200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>482000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>466500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>416700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>398100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>306500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>332600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>347200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>341200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>318000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>329300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>371300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>272800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>312300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>309900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>326800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>344400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>310900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>291600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>338700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>318400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>348800</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1459,8 +1493,14 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1509,11 +1549,11 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1551,35 +1591,41 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>1000</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1619,11 +1665,11 @@
       <c r="O15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1697,8 +1743,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1789,10 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1778,86 +1832,92 @@
       <c r="O17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3">
         <v>14516700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>16238600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16178400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>16105000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>19194100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>17052100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>16186500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>15151300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>16544200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>13954400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>12912000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>10413300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>13614700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>13080200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>12169500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>11436800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>13600700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>13090300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>11732400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>10537600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>12734100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>11673200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>10018300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>9504800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>12030700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>11015800</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1897,86 +1957,92 @@
       <c r="O18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3">
         <v>750000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>850900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>777200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>588800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>932400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>816600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>742700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>478800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>701200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>564500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>435900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>166100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>488100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>441800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>342700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>273500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>434400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>289500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>180300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>100700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>204400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>87700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>73900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>138000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>215400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2084,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,86 +2127,92 @@
       <c r="O20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3">
         <v>-59800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-46500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-24600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-8100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-12100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-6700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-27400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-30100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-36300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-33100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-39700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-34700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-32500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-26200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-23500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-12000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-14100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-9300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>10300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2178,86 +2252,92 @@
       <c r="O21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3">
         <v>1040400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1137900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1084000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>907400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1237700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1123000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1022700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>743300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>924900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>788500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>644500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>406600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>704700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>608500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>529500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>451400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>610700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>474200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>356300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>279800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>382000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>258700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>158500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>247700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>329700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2297,86 +2377,92 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3">
         <v>85100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>94300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>62100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>60600</v>
-      </c>
-      <c r="T22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>67700</v>
       </c>
       <c r="V22" s="3">
         <v>65100</v>
       </c>
       <c r="W22" s="3">
+        <v>67700</v>
+      </c>
+      <c r="X22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>68500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>73400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>61000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>64100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>62800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>63200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>65700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>70100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>67100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>60600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>54200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>55500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>49700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>41600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>43100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>52900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>56100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>46900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>47400</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2416,86 +2502,92 @@
       <c r="O23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3">
         <v>605000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>710100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>690500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>520200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>855200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>742100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>650200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>380300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>591500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>470400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>332100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>77300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>390200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>310100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>240100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>180200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>350300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>213300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>112800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>36800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>150300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>35300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-69300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>15200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>101300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>167800</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2535,86 +2627,92 @@
       <c r="O24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3">
         <v>123100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>156200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>151000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>98800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>173500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>185100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>165100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>95100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>160000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>120800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>85300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>13900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>84700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>66400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>48200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>46700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>85500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>39800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>27500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-11600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>424800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>-117800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>-88500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>15800</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +2830,14 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2773,86 +2877,92 @@
       <c r="O26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3">
         <v>481900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>553800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>539500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>421400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>681700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>557100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>485200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>285200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>431400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>349600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>246800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>63400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>305500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>243600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>191900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>133600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>264800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>173500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>85300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>48400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-274500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>153200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-53900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>103700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>107100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2892,86 +3002,92 @@
       <c r="O27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="3">
         <v>437200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>541200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>515700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>412200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>639600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>512000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>466100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>260200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>395100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>310200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>212800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>42600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>258100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>202200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>162200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>118100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>232800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>168400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>77000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-288800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>139000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-72300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>106900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>98400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3205,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3130,11 +3252,11 @@
       <c r="O29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3208,8 +3330,14 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3455,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3580,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,86 +3627,92 @@
       <c r="O32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3">
         <v>59800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>46500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>24600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>8100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>12100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>6700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>27400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>30100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>36300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>33100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>39700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>26100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>34700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>66000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>32500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>26200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>23500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>22100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>12000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>12500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>9300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>10200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>2500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3606,86 +3752,92 @@
       <c r="O33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R33" s="3">
         <v>437200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>541200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>515700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>412200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>639600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>512000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>466100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>260200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>395100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>310200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>212800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>42600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>258100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>202200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>162200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>118100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>232800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>168400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>77000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-288800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>139000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-72300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>106900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>98400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,8 +3955,14 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3844,210 +4002,222 @@
       <c r="O35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="3">
         <v>437200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>541200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>515700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>412200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>639600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>512000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>466100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>260200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>395100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>310200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>212800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>42600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>258100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>202200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>162200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>118100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>232800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>168400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>77000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-288800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>139000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-72300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>106900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>98400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4259,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,1079 +4304,1135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5907500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4887200</v>
+      </c>
+      <c r="F41" s="3">
         <v>5221400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5112100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4504400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4728100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3934400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4178900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3911100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3559800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3466200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3737000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4354800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4250100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5018900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>5567400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3788100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3930300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3756500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3647500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3175800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3068400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4040100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>3698700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3495600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>3551000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>3520900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>3310900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2717400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2662900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3399900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2212500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2613100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>1848000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>1660300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>1143800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>1387500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>2754600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>2523000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>2253100</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>52400</v>
+      </c>
+      <c r="F42" s="3">
         <v>153000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>131600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>5310800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>58200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>189200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>114500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>113600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>60400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>100800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>118000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>249900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>198000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>61800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>60400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>57600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>92500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>72500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>83500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>82800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>59400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>51100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>54000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>50700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>66500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>65100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>65200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>70600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>70200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>108600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>112300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>75900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>84300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>86500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>118200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>153600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>196700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>162200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AQ42" s="3">
         <v>196600</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26871300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>20638000</v>
+      </c>
+      <c r="F43" s="3">
         <v>19416600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>17970300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>11159700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13760700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>13809500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>13431900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11384500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>10936700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12059400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>11595000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>10125900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>10236200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>11854000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>12346700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>14797200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>15244900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>16798400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>13698200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>13029500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>12518900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>13537100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>11207200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>10257700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>8850900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>12562500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>11648000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>11474800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>9481000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>10010500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>10509900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>10307200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>8557600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>9712800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>9751000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>8075700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>8062800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>8914800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>8875200</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15741900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>11720900</v>
+      </c>
+      <c r="F44" s="3">
         <v>9076600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>8617400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>8742600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>7923800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>9147700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>9118800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>7777600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6702700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>6218900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6169600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>5907200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6371900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>7502100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>8417900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>8867700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>8300700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>8441600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>8727800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>7825800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>6380600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>5785800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>5242300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>5126700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>4946900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3998400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>3816900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>3573000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3434700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>3792300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>4280900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>4125100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>3791700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>3983300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>3600000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>3177500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>2794000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>2833600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>2882800</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>254900</v>
+      </c>
+      <c r="F45" s="3">
         <v>49600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>55500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>43400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>110800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>185600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>29900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>94400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>127600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>15400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>107200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>98900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>97800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1695300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1725700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1594500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1428500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1413800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1414700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1396500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1308100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1036400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1102900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1116900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1318200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1299100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1275600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1172300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>1237500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1168400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1211800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1524900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>1381800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>1502200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>1419700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>1354900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>1060200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>980200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>930100</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50655200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>39202300</v>
+      </c>
+      <c r="F46" s="3">
         <v>35437800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>33216700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>29760900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27904100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>28574500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>28206500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>24557300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>22687200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23227800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>23409200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>22274500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22940900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>26132000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>28118100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>29105000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>28996900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>30482800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>27571700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>25510300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>23335400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>24450500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>21305000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>20047600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>18733400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>21446000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>20116800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>19008100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>16886200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>18479800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>18327500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>18646200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>15663300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>16945200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>16032700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>14149300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>14868400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>15413900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>15137700</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2631900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2347100</v>
+      </c>
+      <c r="F47" s="3">
         <v>2210900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1925600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1856100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1825500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1757000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1843100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1772500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1768400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1718700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1719600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1637400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1738400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1673800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1554800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1543800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1508500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1293600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1193400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1120400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>955300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>939200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>844200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>701700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>611300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>618200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>556300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>554700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>599900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>559700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>506600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>431900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>408700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>392900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>366600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>304700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>288500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>236300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AQ47" s="3">
         <v>215000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3482100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3518800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3320200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3042000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2938300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2900900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2754300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2893100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2831000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2919100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2999300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3157900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3123800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3303900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3174200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2788700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2846700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2986100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2834000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2711600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2657000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2674900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2565700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2555100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2472500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2017100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2016100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1937900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1936400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1662900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1568900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1514700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1636000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1687600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1663500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>1706600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>1716100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>1649400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>1588100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>1593000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8926000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7920700</v>
+      </c>
+      <c r="F49" s="3">
         <v>7921700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8256300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>8328700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>8233000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>8026400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>8257700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>8198800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>8345400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>8519200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>8174800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>8190500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8267100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8184600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>8048700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>7849700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8066800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8138300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8238900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8447600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>8405000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>8152100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>7980100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>7991500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>7984600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>8230900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8196700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>8391500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8324600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>8296700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>8286300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>8426900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>8514500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>8416300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>8448400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>8317200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>8349100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>8313800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>8560500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5550,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5675,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>378300</v>
+      </c>
+      <c r="F52" s="3">
         <v>333200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>310300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>335100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>311400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>417500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>467300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>420100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>397500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>408000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>284700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>210200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>202500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2584100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2783200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2903300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2952200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2897500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2859000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2725300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2620100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2537600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2399800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2281700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2781800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2715100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2581700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2520900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2514900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2373500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2252300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2170400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2220000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>2081500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>2369200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>2139600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>2030600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>1651600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>1578300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5925,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>70112100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>57129100</v>
+      </c>
+      <c r="F54" s="3">
         <v>52632400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>49831200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>46323200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>44230800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>44722300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>44464300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>40484700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>38751000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>39504300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>39256700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>37924400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>38920100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>41748600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>43293500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>44248500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>44510400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>45646200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>42574700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>40460600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>37990600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>38645100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>35084200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>33495000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>32128200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>35026300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>33389400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>32411600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>29988500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>31278600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>30887400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>31311400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>28494200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>29499400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>28923600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>26626800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>27186000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>27203800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>27084500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +6099,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6144,760 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24397600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>19236700</v>
+      </c>
+      <c r="F57" s="3">
         <v>16727000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>16132400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>14187800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11978900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13883800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14229400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11924600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>10505400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10258500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>10872300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9284200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>9772900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>10837300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>12348700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>13609600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11035900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>12516700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>11492000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>11198200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>10220800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>9968000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8525700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7806100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7509700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>8665800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7857700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>6736700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>6429800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7339800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>7281900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>7919600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>6450800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>7498200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>7240100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>6209100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>5649900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>6162700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>5758900</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>996600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>988500</v>
+      </c>
+      <c r="F58" s="3">
         <v>299300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>146100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>159700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1125300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1147100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1120100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1100500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>152000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>176100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>414300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>398800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>395300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>736500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>753100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>963300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3081900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1637700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1856900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1853800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1717600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1987100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3508300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3895400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>4845600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3966000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3901700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>4094900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3225900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>3675300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>3259700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>3470000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>1968700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>1004200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>1055400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>905600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>700600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AQ58" s="3">
         <v>708200</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20771200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>16004200</v>
+      </c>
+      <c r="F59" s="3">
         <v>15386300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>14171100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13102900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>12498600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13630400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13446700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12443900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>12074400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13078100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>12621300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>12570400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12361500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>17343400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>17673600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>18396800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>18640900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>19546000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>17995800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>16166600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>15433300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>15165700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>12541100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>11673600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>10902800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>12601600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>12280300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>12013500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>10834600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>11768900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>12050400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>11625600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>11040300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>12086600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>12009800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>10788000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>11778300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>12984600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>11364000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51795800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>41357600</v>
+      </c>
+      <c r="F60" s="3">
         <v>36890400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>34516000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>31285100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>29994100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>32904100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>32682100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>28839000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>26059200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>26700700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>27055700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>25378000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>26093400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>28917200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>30775300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>32969700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>32758700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>33700300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>31344700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>29218600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>27371600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>27120700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>24575100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>23375100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>23258100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>25233500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>24039700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>22845100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>20490300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>22784100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>22592000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>23015300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>19459700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>20589000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>20295000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>18052500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>18333800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>19848000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>17831000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5669500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4168000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4753100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4693000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4663400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4607600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2834200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2830700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2833100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3809700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3826700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3907300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3972800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3964000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4180700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4185100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2890000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2896300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3619300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3627000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3622000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3632800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4246500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2873000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2867400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1911400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2498400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2452800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2462800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2426800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1821200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1820100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1842200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>2648700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>2617700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>2591300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>2579200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>2966700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>2465200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>2487500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1647100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>542500</v>
+      </c>
+      <c r="F62" s="3">
         <v>595700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>743600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>619100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>750800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>471000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>520500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>504600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>574400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>616000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>584800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>591500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>642700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2847200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2706100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2803700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3460800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3534700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3464100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3460000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3375600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3367000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3179700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3022200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2899300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2999200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2882400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>2846900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2974300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>2803400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>2521900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>2115800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>1839700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>1916700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>1848900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>1817100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>1790200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>1856000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>3583200</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +7015,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +7140,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7265,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61944400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>48685500</v>
+      </c>
+      <c r="F66" s="3">
         <v>44786300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>42342300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>38882300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>37570900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>38581400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>38372800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>34419300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>32669800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>33391300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>33678200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>32067400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>32873000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>36424100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>38109200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>39068600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>39519800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>41162200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>38571700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>36400300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>34431600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>34758400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>30568500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>29159200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>27937000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>30588700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>29147100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>27899500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>25598400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>27099800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>26872400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>26971200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>23981900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>25154000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>24769900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>22489200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>23118700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>24201600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>23923100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7439,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7560,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7685,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7810,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7935,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6218600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>7250000</v>
+      </c>
+      <c r="F72" s="3">
         <v>6715200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6318200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>6457400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>5971600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5875400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5319200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5435400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>5207100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4969500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4753600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4963400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4805900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4590200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>4209700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>4064400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3841000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3460100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2951300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2796200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2334600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2056000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1803600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1825700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1614800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1603800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1453200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1586700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1424000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1249300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1110200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1242900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1160100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1531400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>1684100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>1756400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>1616600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8185,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8310,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8435,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6666000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7087700</v>
+      </c>
+      <c r="F76" s="3">
         <v>6524200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6294600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6259600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5521600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5028700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4930000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5015200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5035200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5053100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4579800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4861800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5040200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5324600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5184300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5179900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4990600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4484000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4003000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4060400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3559000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3886800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4515700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>4335800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>4191200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>4437600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>4242300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>4512100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>4390100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>4178800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>4015000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>4340200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>4512300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>4345400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>4153700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>4137600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>4067300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>3002200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>3161400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,132 +8685,144 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8472,86 +8862,92 @@
       <c r="O81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R81" s="3">
         <v>437200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>541200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>515700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>412200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>639600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>512000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>466100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>260200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>395100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>310200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>212800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>42600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>258100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>202200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>162200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>118100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>232800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>168400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>77000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-288800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>139000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-72300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>106900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>98400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8989,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>143600</v>
+      </c>
+      <c r="F83" s="3">
         <v>148400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>141600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>136200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>155800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>141000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>140600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>143800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>143800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>135000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>123600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>126300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>129300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>350300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>333500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>331400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>326600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>317400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>313100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>307300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>294600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>260000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>257100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>248300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>266500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>251200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>232700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>219300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>204100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>199800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>206800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>188000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>193300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>190100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>180300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>174900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>176400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>181400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>191300</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9235,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9360,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9485,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9610,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9735,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>382300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>309800</v>
+      </c>
+      <c r="F89" s="3">
         <v>951800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1543000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1219100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1022400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>344100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>986700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>791400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>543300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>364200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>453800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>649800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>244400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>74000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2084300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>398700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1462500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>606300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1560600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>447600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>601400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1962900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>771400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>317100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>431600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>538300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1381600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-141600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-478100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1547600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>67100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>336000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-753500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>210900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>363600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-577400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>207600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>345500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>1558700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9909,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-206200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-393900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-404800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-286200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-177000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-185400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-174300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-152200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-154500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-204400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-158900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-191600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-174800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-278900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-383400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-383400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-386200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-364500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-361800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-278500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-279300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-111400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-71600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-69600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-50200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-71900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-31200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-76200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-86400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-177300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-181700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-154700</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +10155,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10280,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-880400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-539400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-590900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-358100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-420800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-196300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-335200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-204900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-319800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-250300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-364400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-468700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-200000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-314000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-407200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-806000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-387800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-574100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-389300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-343400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-191600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-279600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-197000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-214300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-285100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-237800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-215400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-200400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-303400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-181500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-217100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-103700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-197400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-173500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-92900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-743900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-1323900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>93100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-200800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,127 +10454,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>134100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>478400</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>134000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>474300</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>124500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>458800</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-123400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-119800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-102000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-96400</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-91400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-92300</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-85100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10700,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10825,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10950,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1504700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-110500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-237400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-562300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1087200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1963300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-99100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-627000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-47200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-154500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-323400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-574900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-283400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-729100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-301500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>625300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-8500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-750100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-110400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-717100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-179800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1224700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1524500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-387900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-91100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-69000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-157600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-524100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>512300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-165100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-317800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>691600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1071600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>395000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-525700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>1318500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-1014900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>49100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-154200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>113100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-73100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-44800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>52800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-28000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>29900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>29900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>86200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-124300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-144700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>35600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>86200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-124300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-144700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>35600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-28500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>31100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-68900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>100100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>33800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>3700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-94800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>44700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-63500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>8500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>22000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-46200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>13700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>11400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>20600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>29300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-50800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AQ101" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1020300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-334200</v>
+      </c>
+      <c r="F102" s="3">
         <v>109300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>607700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-223700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>793700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-244500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>267800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>351300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>93700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-270800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-617800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>104700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-768800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-548500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1779300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-142200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>173800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>109000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>471700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>107400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-971800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>341500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>203000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-55400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>30100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>210000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>593500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>54600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-737000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1187300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-400600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>765100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>187700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>516500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-243600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-1367100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>231600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>270000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>346900</v>
       </c>
     </row>
